--- a/docker/rsdm/template.xlsx
+++ b/docker/rsdm/template.xlsx
@@ -27,21 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>样方名称</t>
   </si>
   <si>
-    <t>坐标点1</t>
-  </si>
-  <si>
-    <t>坐标点2</t>
-  </si>
-  <si>
-    <t>坐标点3</t>
-  </si>
-  <si>
-    <t>坐标点4</t>
+    <t>坐标点</t>
   </si>
   <si>
     <t>坐标中心点</t>
@@ -1191,7 +1182,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.4166666666667" customWidth="1"/>
-    <col min="2" max="34" width="18.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="39.8888888888889" customWidth="1"/>
+    <col min="3" max="31" width="18.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:34">
@@ -1204,99 +1196,93 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="7" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="U1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="V1" s="8" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Y1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AB1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AC1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AD1" s="9" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="9" t="s">
-        <v>33</v>
-      </c>
+      <c r="AF1"/>
+      <c r="AG1"/>
+      <c r="AH1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docker/rsdm/template.xlsx
+++ b/docker/rsdm/template.xlsx
@@ -27,9 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>样方名称</t>
+  </si>
+  <si>
+    <t>文件名</t>
   </si>
   <si>
     <t>坐标点</t>
@@ -521,7 +524,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -548,6 +551,19 @@
       <left style="medium">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -681,7 +697,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -693,34 +709,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -805,10 +821,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1178,111 +1197,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.4166666666667" customWidth="1"/>
-    <col min="2" max="2" width="39.8888888888889" customWidth="1"/>
-    <col min="3" max="31" width="18.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="19.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="39.8888888888889" customWidth="1"/>
+    <col min="4" max="32" width="18.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:34">
+    <row r="1" s="1" customFormat="1" ht="22.5" customHeight="1" spans="1:35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="S1" s="8" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="U1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="V1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="W1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="X1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Z1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AA1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="9" t="s">
+      <c r="AB1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AC1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AD1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="9" t="s">
+      <c r="AE1" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="AF1"/>
+      <c r="AF1" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="AG1"/>
       <c r="AH1"/>
+      <c r="AI1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
